--- a/outputs/13284.xlsx
+++ b/outputs/13284.xlsx
@@ -759,7 +759,7 @@
         <v>123</v>
       </c>
       <c r="E2" s="7" t="str">
-        <f aca="false" t="array" ref="E2:E2">IF(D2="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C2)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D2&gt;=Streets!$C$2:$C$26)*(D2&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C2)*(Streets!$C$2:$C$26&lt;=D2)*(Streets!$D$2:$D$26&gt;=D2),0)),"")</f>
         <v>Paulo Mauricio</v>
       </c>
       <c r="F2" s="8"/>
@@ -778,7 +778,7 @@
         <v>678</v>
       </c>
       <c r="E3" s="7" t="str">
-        <f aca="false" t="array" ref="E3:E3">IF(D3="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C3)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D3&gt;=Streets!$C$2:$C$26)*(D3&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C3)*(Streets!$C$2:$C$26&lt;=D3)*(Streets!$D$2:$D$26&gt;=D3),0)),"")</f>
         <v>Mario</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -799,7 +799,7 @@
         <v>1237</v>
       </c>
       <c r="E4" s="7" t="str">
-        <f aca="false" t="array" ref="E4:E4">IF(D4="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C4)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D4&gt;=Streets!$C$2:$C$26)*(D4&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C4)*(Streets!$C$2:$C$26&lt;=D4)*(Streets!$D$2:$D$26&gt;=D4),0)),"")</f>
         <v>Celia</v>
       </c>
       <c r="F4" s="8" t="s">
@@ -820,7 +820,7 @@
         <v>2354</v>
       </c>
       <c r="E5" s="7" t="str">
-        <f aca="false" t="array" ref="E5:E5">IF(D5="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C5)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D5&gt;=Streets!$C$2:$C$26)*(D5&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C5)*(Streets!$C$2:$C$26&lt;=D5)*(Streets!$D$2:$D$26&gt;=D5),0)),"")</f>
         <v/>
       </c>
       <c r="F5" s="8" t="s">
@@ -841,7 +841,7 @@
         <v>321</v>
       </c>
       <c r="E6" s="7" t="str">
-        <f aca="false" t="array" ref="E6:E6">IF(D6="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C6)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D6&gt;=Streets!$C$2:$C$26)*(D6&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C6)*(Streets!$C$2:$C$26&lt;=D6)*(Streets!$D$2:$D$26&gt;=D6),0)),"")</f>
         <v>Paulo Ozava</v>
       </c>
       <c r="F6" s="8"/>
@@ -860,7 +860,7 @@
         <v>864</v>
       </c>
       <c r="E7" s="7" t="str">
-        <f aca="false" t="array" ref="E7:E7">IF(D7="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C7)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D7&gt;=Streets!$C$2:$C$26)*(D7&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C7)*(Streets!$C$2:$C$26&lt;=D7)*(Streets!$D$2:$D$26&gt;=D7),0)),"")</f>
         <v>Marilia Luz</v>
       </c>
       <c r="F7" s="8" t="s">
@@ -881,7 +881,7 @@
         <v>920</v>
       </c>
       <c r="E8" s="7" t="str">
-        <f aca="false" t="array" ref="E8:E8">IF(D8="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C8)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D8&gt;=Streets!$C$2:$C$26)*(D8&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C8)*(Streets!$C$2:$C$26&lt;=D8)*(Streets!$D$2:$D$26&gt;=D8),0)),"")</f>
         <v/>
       </c>
       <c r="F8" s="8" t="s">
@@ -902,7 +902,7 @@
         <v>159</v>
       </c>
       <c r="E9" s="7" t="str">
-        <f aca="false" t="array" ref="E9:E9">IF(D9="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C9)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D9&gt;=Streets!$C$2:$C$26)*(D9&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C9)*(Streets!$C$2:$C$26&lt;=D9)*(Streets!$D$2:$D$26&gt;=D9),0)),"")</f>
         <v>Zila</v>
       </c>
       <c r="F9" s="8"/>
@@ -921,7 +921,7 @@
         <v>820</v>
       </c>
       <c r="E10" s="7" t="str">
-        <f aca="false" t="array" ref="E10:E10">IF(D10="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C10)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D10&gt;=Streets!$C$2:$C$26)*(D10&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C10)*(Streets!$C$2:$C$26&lt;=D10)*(Streets!$D$2:$D$26&gt;=D10),0)),"")</f>
         <v/>
       </c>
       <c r="F10" s="8" t="s">
@@ -942,7 +942,7 @@
         <v>468</v>
       </c>
       <c r="E11" s="7" t="str">
-        <f aca="false" t="array" ref="E11:E11">IF(D11="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C11)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D11&gt;=Streets!$C$2:$C$26)*(D11&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C11)*(Streets!$C$2:$C$26&lt;=D11)*(Streets!$D$2:$D$26&gt;=D11),0)),"")</f>
         <v>Laura</v>
       </c>
       <c r="F11" s="8"/>
@@ -961,7 +961,7 @@
         <v>915</v>
       </c>
       <c r="E12" s="7" t="str">
-        <f aca="false" t="array" ref="E12:E12">IF(D12="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C12)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D12&gt;=Streets!$C$2:$C$26)*(D12&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C12)*(Streets!$C$2:$C$26&lt;=D12)*(Streets!$D$2:$D$26&gt;=D12),0)),"")</f>
         <v>Romulo</v>
       </c>
       <c r="F12" s="8" t="s">
@@ -982,7 +982,7 @@
         <v>1179</v>
       </c>
       <c r="E13" s="7" t="str">
-        <f aca="false" t="array" ref="E13:E13">IF(D13="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C13)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D13&gt;=Streets!$C$2:$C$26)*(D13&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C13)*(Streets!$C$2:$C$26&lt;=D13)*(Streets!$D$2:$D$26&gt;=D13),0)),"")</f>
         <v/>
       </c>
       <c r="F13" s="8" t="s">
@@ -1003,7 +1003,7 @@
         <v>1289</v>
       </c>
       <c r="E14" s="9" t="str">
-        <f aca="false" t="array" ref="E14:E14">IF(D14="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C14)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D14&gt;=Streets!$C$2:$C$26)*(D14&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C14)*(Streets!$C$2:$C$26&lt;=D14)*(Streets!$D$2:$D$26&gt;=D14),0)),"")</f>
         <v>Everaldo</v>
       </c>
       <c r="F14" s="8" t="s">
@@ -1024,7 +1024,7 @@
         <v>1414</v>
       </c>
       <c r="E15" s="9" t="str">
-        <f aca="false" t="array" ref="E15:E15">IF(D15="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C15)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D15&gt;=Streets!$C$2:$C$26)*(D15&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C15)*(Streets!$C$2:$C$26&lt;=D15)*(Streets!$D$2:$D$26&gt;=D15),0)),"")</f>
         <v>Domingos</v>
       </c>
       <c r="F15" s="8" t="s">
@@ -1045,7 +1045,7 @@
         <v>1691</v>
       </c>
       <c r="E16" s="9" t="str">
-        <f aca="false" t="array" ref="E16:E16">IF(D16="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C16)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D16&gt;=Streets!$C$2:$C$26)*(D16&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C16)*(Streets!$C$2:$C$26&lt;=D16)*(Streets!$D$2:$D$26&gt;=D16),0)),"")</f>
         <v/>
       </c>
       <c r="F16" s="8" t="s">
@@ -1066,7 +1066,7 @@
         <v>253</v>
       </c>
       <c r="E17" s="7" t="str">
-        <f aca="false" t="array" ref="E17:E17">IF(D17="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C17)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D17&gt;=Streets!$C$2:$C$26)*(D17&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C17)*(Streets!$C$2:$C$26&lt;=D17)*(Streets!$D$2:$D$26&gt;=D17),0)),"")</f>
         <v/>
       </c>
       <c r="F17" s="8"/>
@@ -1085,7 +1085,7 @@
         <v>681</v>
       </c>
       <c r="E18" s="7" t="str">
-        <f aca="false" t="array" ref="E18:E18">IF(D18="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C18)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D18&gt;=Streets!$C$2:$C$26)*(D18&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C18)*(Streets!$C$2:$C$26&lt;=D18)*(Streets!$D$2:$D$26&gt;=D18),0)),"")</f>
         <v/>
       </c>
       <c r="F18" s="8"/>
@@ -1104,7 +1104,7 @@
         <v>37</v>
       </c>
       <c r="E19" s="7" t="str">
-        <f aca="false" t="array" ref="E19:E19">IF(D19="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C19)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D19&gt;=Streets!$C$2:$C$26)*(D19&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C19)*(Streets!$C$2:$C$26&lt;=D19)*(Streets!$D$2:$D$26&gt;=D19),0)),"")</f>
         <v/>
       </c>
       <c r="F19" s="8"/>
@@ -1123,7 +1123,7 @@
         <v>1247</v>
       </c>
       <c r="E20" s="7" t="str">
-        <f aca="false" t="array" ref="E20:E20">IF(D20="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C20)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D20&gt;=Streets!$C$2:$C$26)*(D20&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C20)*(Streets!$C$2:$C$26&lt;=D20)*(Streets!$D$2:$D$26&gt;=D20),0)),"")</f>
         <v/>
       </c>
       <c r="F20" s="8"/>
@@ -1142,7 +1142,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="7" t="str">
-        <f aca="false" t="array" ref="E21:E21">IF(D21="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C21)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D21&gt;=Streets!$C$2:$C$26)*(D21&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C21)*(Streets!$C$2:$C$26&lt;=D21)*(Streets!$D$2:$D$26&gt;=D21),0)),"")</f>
         <v/>
       </c>
       <c r="F21" s="8"/>
@@ -1161,7 +1161,7 @@
         <v>1001</v>
       </c>
       <c r="E22" s="7" t="str">
-        <f aca="false" t="array" ref="E22:E22">IF(D22="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C22)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D22&gt;=Streets!$C$2:$C$26)*(D22&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C22)*(Streets!$C$2:$C$26&lt;=D22)*(Streets!$D$2:$D$26&gt;=D22),0)),"")</f>
         <v/>
       </c>
       <c r="F22" s="8"/>
@@ -1180,7 +1180,7 @@
         <v>876</v>
       </c>
       <c r="E23" s="7" t="str">
-        <f aca="false" t="array" ref="E23:E23">IF(D23="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C23)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D23&gt;=Streets!$C$2:$C$26)*(D23&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C23)*(Streets!$C$2:$C$26&lt;=D23)*(Streets!$D$2:$D$26&gt;=D23),0)),"")</f>
         <v/>
       </c>
       <c r="F23" s="8"/>
@@ -1199,7 +1199,7 @@
         <v>305</v>
       </c>
       <c r="E24" s="7" t="str">
-        <f aca="false" t="array" ref="E24:E24">IF(D24="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C24)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D24&gt;=Streets!$C$2:$C$26)*(D24&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C24)*(Streets!$C$2:$C$26&lt;=D24)*(Streets!$D$2:$D$26&gt;=D24),0)),"")</f>
         <v/>
       </c>
       <c r="F24" s="8"/>
@@ -1218,7 +1218,7 @@
         <v>95</v>
       </c>
       <c r="E25" s="7" t="str">
-        <f aca="false" t="array" ref="E25:E25">IF(D25="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C25)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D25&gt;=Streets!$C$2:$C$26)*(D25&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C25)*(Streets!$C$2:$C$26&lt;=D25)*(Streets!$D$2:$D$26&gt;=D25),0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="8"/>
@@ -1237,7 +1237,7 @@
         <v>431</v>
       </c>
       <c r="E26" s="7" t="str">
-        <f aca="false" t="array" ref="E26:E26">IF(D26="","",IFERROR(_xlfn.XLOOKUP(1,(Streets!$B$2:$B$26=C26)*(Streets!$C$2:$C$26&lt;&gt;"")*(Streets!$D$2:$D$26&lt;&gt;"")*(D26&gt;=Streets!$C$2:$C$26)*(D26&lt;=Streets!$D$2:$D$26),Streets!$F$2:$F$26),""))</f>
+        <f aca="false">IFERROR(INDEX(Streets!$F$2:$F$26,MATCH(1,(Streets!$B$2:$B$26=C26)*(Streets!$C$2:$C$26&lt;=D26)*(Streets!$D$2:$D$26&gt;=D26),0)),"")</f>
         <v/>
       </c>
       <c r="F26" s="8"/>
